--- a/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation-complete.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation-complete.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="831">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -399,6 +399,12 @@
   </si>
   <si>
     <t>Salmonella sp identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>17576-0</t>
+  </si>
+  <si>
+    <t>Shigella sp identified in Specimen by Organism specific culture</t>
   </si>
   <si>
     <t>17735-2</t>
@@ -2767,7 +2773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B386"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5843,15 +5849,23 @@
         <v>794</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>796</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>798</v>
       </c>
     </row>
   </sheetData>
@@ -5878,58 +5892,58 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -5956,98 +5970,98 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation-complete.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation-complete.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1235,6 +1235,12 @@
     <t>Neisseria gonorrhoeae rRNA [Presence] in Vaginal fluid by NAA with probe detection</t>
   </si>
   <si>
+    <t>539-7</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp identified in Sputum by Organism specific culture</t>
+  </si>
+  <si>
     <t>53917-1</t>
   </si>
   <si>
@@ -1275,12 +1281,6 @@
   </si>
   <si>
     <t>Escherichia coli shiga-like toxin identified in Specimen</t>
-  </si>
-  <si>
-    <t>539-7</t>
-  </si>
-  <si>
-    <t>Mycobacterium sp identified in Sputum by Organism specific culture</t>
   </si>
   <si>
     <t>540-5</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation-complete.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation-complete.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="945">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -155,6 +155,12 @@
     <t>Legionella sp DNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>101298-8</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Throat by NAA with non-probe detection</t>
+  </si>
+  <si>
     <t>101307-7</t>
   </si>
   <si>
@@ -281,6 +287,18 @@
     <t>Shigella species+EIEC invasion plasmid antigen H ipaH gene [Presence] in Specimen</t>
   </si>
   <si>
+    <t>105211-7</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchial specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>105231-5</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Sputum by NAA with probe detection</t>
+  </si>
+  <si>
     <t>105640-7</t>
   </si>
   <si>
@@ -299,6 +317,18 @@
     <t>Tick-borne encephalitis virus Ab [Interpretation] in Serum or Plasma</t>
   </si>
   <si>
+    <t>108111-6</t>
+  </si>
+  <si>
+    <t>Hantavirus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>111556-7</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchoalveolar aspirate by NAA with non-probe detection</t>
+  </si>
+  <si>
     <t>11259-9</t>
   </si>
   <si>
@@ -893,6 +923,12 @@
     <t>Influenza virus B RNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>40988-8</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>41216-3</t>
   </si>
   <si>
@@ -1697,6 +1733,18 @@
     <t>Influenza virus B RNA [Presence] in Nasopharynx by NAA with probe detection</t>
   </si>
   <si>
+    <t>76088-4</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchoalveolar lavage by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>76089-2</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Nasopharynx by NAA with probe detection</t>
+  </si>
+  <si>
     <t>76626-1</t>
   </si>
   <si>
@@ -1895,6 +1943,12 @@
     <t>Influenza virus B RNA [Presence] in Upper respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>85479-4</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Upper respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>85622-9</t>
   </si>
   <si>
@@ -2087,6 +2141,12 @@
     <t>Measles virus RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>91133-9</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>91780-7</t>
   </si>
   <si>
@@ -2123,6 +2183,12 @@
     <t>Middle East respiratory syndrome coronavirus (MERS-CoV) RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>92131-2</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Respiratory system specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>92141-1</t>
   </si>
   <si>
@@ -2442,6 +2508,282 @@
   </si>
   <si>
     <t>Human immunodeficiency virus type I (organism)</t>
+  </si>
+  <si>
+    <t>1087501000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Buttiauxella</t>
+  </si>
+  <si>
+    <t>1089101000112105</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter amalonaticus</t>
+  </si>
+  <si>
+    <t>1089301000112107</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter braakii</t>
+  </si>
+  <si>
+    <t>1089501000112101</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter</t>
+  </si>
+  <si>
+    <t>1089701000112106</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter farmeri</t>
+  </si>
+  <si>
+    <t>1089901000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter freundii</t>
+  </si>
+  <si>
+    <t>1090201000112105</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter gillenii</t>
+  </si>
+  <si>
+    <t>1090401000112109</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter koseri</t>
+  </si>
+  <si>
+    <t>1090601000112107</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter murliniae</t>
+  </si>
+  <si>
+    <t>1091001000112109</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter sedlakii</t>
+  </si>
+  <si>
+    <t>1091201000112104</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter werkmanii</t>
+  </si>
+  <si>
+    <t>1091401000112100</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter youngae</t>
+  </si>
+  <si>
+    <t>1092401000112105</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Cronobacter sakazakii</t>
+  </si>
+  <si>
+    <t>1093401000112101</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter</t>
+  </si>
+  <si>
+    <t>1093601000112103</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter asburiae</t>
+  </si>
+  <si>
+    <t>1094301000112105</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter hormaechei</t>
+  </si>
+  <si>
+    <t>1096801000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella</t>
+  </si>
+  <si>
+    <t>1097701000112102</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella pneumoniae subsp. ozaenae</t>
+  </si>
+  <si>
+    <t>1098201000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella pneumoniae</t>
+  </si>
+  <si>
+    <t>1099001000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera</t>
+  </si>
+  <si>
+    <t>1099201000112103</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera ascorbata</t>
+  </si>
+  <si>
+    <t>1099401000112104</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera cryocrescens</t>
+  </si>
+  <si>
+    <t>1099601000112101</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera georgiana</t>
+  </si>
+  <si>
+    <t>1099801000112102</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Kluyvera intermedia</t>
+  </si>
+  <si>
+    <t>1100001000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Leclercia</t>
+  </si>
+  <si>
+    <t>1100201000112103</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Leclercia adecarboxylata</t>
+  </si>
+  <si>
+    <t>1105401000112106</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Raoultella ornithinolytica</t>
+  </si>
+  <si>
+    <t>1105601000112109</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Raoultella planticola</t>
+  </si>
+  <si>
+    <t>1105801000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Raoultella terrigena</t>
+  </si>
+  <si>
+    <t>1106001000112106</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Salmonella</t>
+  </si>
+  <si>
+    <t>1108301000112108</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Shigella</t>
+  </si>
+  <si>
+    <t>1112101000112106</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Lelliottia amnigena</t>
+  </si>
+  <si>
+    <t>1359810002</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Cronobacter</t>
+  </si>
+  <si>
+    <t>1359811003</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Escherichia spp</t>
+  </si>
+  <si>
+    <t>1362138006</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Lelliottia</t>
+  </si>
+  <si>
+    <t>1388125003</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Pluralibacter (organism)</t>
+  </si>
+  <si>
+    <t>308241000087107</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Pluralibacter gergoviae (organism)</t>
+  </si>
+  <si>
+    <t>33691000087101</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella variicola</t>
+  </si>
+  <si>
+    <t>432763001</t>
+  </si>
+  <si>
+    <t>Enterobacter ludwigii (organism)</t>
+  </si>
+  <si>
+    <t>44601000087107</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Citrobacter freundii complex</t>
+  </si>
+  <si>
+    <t>51271000087100</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella oxytoca</t>
+  </si>
+  <si>
+    <t>734352006</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Klebsiella aerogenes (organism)</t>
+  </si>
+  <si>
+    <t>734353001</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter cloacae complex (organism)</t>
+  </si>
+  <si>
+    <t>737528008</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Escherichia coli (organism)</t>
+  </si>
+  <si>
+    <t>737529000</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Enterobacter cloacae (organism)</t>
+  </si>
+  <si>
+    <t>770392005</t>
+  </si>
+  <si>
+    <t>Carbapenemase-producing Raoultella (organism)</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
@@ -2773,7 +3115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5857,15 +6199,103 @@
         <v>796</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B388" t="s" s="2">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B389" t="s" s="2">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B390" t="s" s="2">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B391" t="s" s="2">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B394" t="s" s="2">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B395" t="s" s="2">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B396" t="s" s="2">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B397" t="s" s="2">
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -5875,7 +6305,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5892,58 +6322,426 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>800</v>
+        <v>822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>801</v>
+        <v>823</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>802</v>
+        <v>824</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>804</v>
+        <v>826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>805</v>
+        <v>827</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>806</v>
+        <v>828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>807</v>
+        <v>829</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>808</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>796</v>
+        <v>831</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>796</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>797</v>
+        <v>833</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>809</v>
+        <v>834</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -5970,98 +6768,98 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>810</v>
+        <v>924</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>811</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>812</v>
+        <v>926</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>813</v>
+        <v>927</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>814</v>
+        <v>928</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>815</v>
+        <v>929</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>816</v>
+        <v>930</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>817</v>
+        <v>931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>818</v>
+        <v>932</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>819</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>820</v>
+        <v>934</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>821</v>
+        <v>935</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>822</v>
+        <v>936</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>823</v>
+        <v>937</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>824</v>
+        <v>938</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>825</v>
+        <v>939</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>826</v>
+        <v>940</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>827</v>
+        <v>941</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>828</v>
+        <v>942</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>829</v>
+        <v>943</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>796</v>
+        <v>818</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>796</v>
+        <v>818</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>797</v>
+        <v>819</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>830</v>
+        <v>944</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation-complete.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation-complete.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
